--- a/Team-Data/2007-08/3-18-2007-08.xlsx
+++ b/Team-Data/2007-08/3-18-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -805,7 +872,7 @@
         <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
         <v>11</v>
@@ -814,7 +881,7 @@
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
         <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="H3" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I3" t="n">
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L3" t="n">
         <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="P3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U3" t="n">
         <v>22.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
         <v>4.6</v>
@@ -912,16 +979,16 @@
         <v>22.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -945,13 +1012,13 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
@@ -960,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1139,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
         <v>30</v>
@@ -1163,7 +1230,7 @@
         <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
@@ -1178,7 +1245,7 @@
         <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.403</v>
+        <v>0.394</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
         <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.359</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
         <v>18.6</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
         <v>0.746</v>
@@ -1252,13 +1319,13 @@
         <v>13.4</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V5" t="n">
         <v>14.5</v>
@@ -1267,25 +1334,25 @@
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1297,10 +1364,10 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1315,13 +1382,13 @@
         <v>23</v>
       </c>
       <c r="AN5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
         <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1339,7 +1406,7 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1354,13 +1421,13 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1573,7 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1521,7 +1588,7 @@
         <v>25</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>16</v>
@@ -1533,7 +1600,7 @@
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="n">
         <v>44</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.647</v>
+        <v>0.657</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J7" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L7" t="n">
         <v>6</v>
@@ -1604,16 +1671,16 @@
         <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P7" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8149999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S7" t="n">
         <v>32.3</v>
@@ -1625,46 +1692,46 @@
         <v>20.7</v>
       </c>
       <c r="V7" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
         <v>6.1</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>21.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB7" t="n">
         <v>100.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1679,10 +1746,10 @@
         <v>18</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1724,7 +1791,7 @@
         <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
         <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,10 +1838,10 @@
         <v>39.6</v>
       </c>
       <c r="J8" t="n">
-        <v>85.3</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L8" t="n">
         <v>6.7</v>
@@ -1783,7 +1850,7 @@
         <v>19</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
         <v>23</v>
@@ -1795,25 +1862,25 @@
         <v>0.755</v>
       </c>
       <c r="R8" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>44.3</v>
+        <v>44.6</v>
       </c>
       <c r="U8" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="V8" t="n">
         <v>15.1</v>
       </c>
       <c r="W8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X8" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
@@ -1825,13 +1892,13 @@
         <v>23.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>109</v>
+        <v>108.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,13 +1910,13 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
         <v>8</v>
@@ -1858,10 +1925,10 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1885,19 +1952,19 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -1935,85 +2002,85 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.461</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
         <v>16.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0.762</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S9" t="n">
         <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U9" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="V9" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="W9" t="n">
         <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA9" t="n">
         <v>20.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,16 +2092,16 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
         <v>13</v>
@@ -2058,13 +2125,13 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
         <v>22</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2079,13 +2146,13 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" t="n">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.621</v>
+        <v>0.631</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="J10" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L10" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M10" t="n">
         <v>27</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T10" t="n">
         <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W10" t="n">
         <v>9.1</v>
@@ -2183,25 +2250,25 @@
         <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AA10" t="n">
         <v>21.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.9</v>
+        <v>111</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2225,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>15</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2243,16 +2310,16 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
         <v>19</v>
@@ -2264,7 +2331,7 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
         <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.697</v>
       </c>
       <c r="H11" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J11" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L11" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O11" t="n">
         <v>16</v>
@@ -2338,19 +2405,19 @@
         <v>22.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="R11" t="n">
         <v>12.1</v>
       </c>
       <c r="S11" t="n">
-        <v>32.5</v>
+        <v>32.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V11" t="n">
         <v>14.2</v>
@@ -2371,13 +2438,13 @@
         <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>3</v>
@@ -2392,10 +2459,10 @@
         <v>23</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
         <v>16</v>
@@ -2422,7 +2489,7 @@
         <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
         <v>15</v>
@@ -2443,16 +2510,16 @@
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2598,7 +2665,7 @@
         <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2619,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-6.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2804,7 +2871,7 @@
         <v>15</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -2845,34 +2912,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I14" t="n">
         <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="N14" t="n">
         <v>0.373</v>
@@ -2890,7 +2957,7 @@
         <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="T14" t="n">
         <v>44.1</v>
@@ -2908,7 +2975,7 @@
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.7</v>
@@ -2920,19 +2987,19 @@
         <v>107.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -2941,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3123,7 +3190,7 @@
         <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>18</v>
@@ -3135,13 +3202,13 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3171,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -3209,22 +3276,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
         <v>54</v>
       </c>
       <c r="G16" t="n">
-        <v>0.182</v>
+        <v>0.169</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J16" t="n">
         <v>78</v>
@@ -3233,34 +3300,34 @@
         <v>0.455</v>
       </c>
       <c r="L16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M16" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
         <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.719</v>
+        <v>0.72</v>
       </c>
       <c r="R16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="T16" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="U16" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V16" t="n">
         <v>14.9</v>
@@ -3275,19 +3342,19 @@
         <v>3.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA16" t="n">
         <v>20.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.7</v>
+        <v>-7.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3311,13 +3378,13 @@
         <v>14</v>
       </c>
       <c r="AL16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM16" t="n">
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3344,7 +3411,7 @@
         <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J17" t="n">
         <v>81.5</v>
@@ -3415,25 +3482,25 @@
         <v>0.447</v>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.736</v>
+        <v>0.739</v>
       </c>
       <c r="R17" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
         <v>28.4</v>
@@ -3445,7 +3512,7 @@
         <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>6.5</v>
@@ -3460,34 +3527,34 @@
         <v>21.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
         <v>19</v>
@@ -3502,7 +3569,7 @@
         <v>26</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3520,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3529,16 +3596,16 @@
         <v>23</v>
       </c>
       <c r="AX17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>22</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3669,13 +3736,13 @@
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
@@ -3705,7 +3772,7 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>11</v>
@@ -3723,7 +3790,7 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
         <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3785,16 +3852,16 @@
         <v>16.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O19" t="n">
         <v>20.1</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R19" t="n">
         <v>11.5</v>
@@ -3803,10 +3870,10 @@
         <v>30.9</v>
       </c>
       <c r="T19" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V19" t="n">
         <v>15.2</v>
@@ -3818,34 +3885,34 @@
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB19" t="n">
         <v>94.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.3</v>
+        <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3881,16 +3948,16 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV19" t="n">
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3905,10 +3972,10 @@
         <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>5.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4090,7 +4157,7 @@
         <v>12</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4242,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>16</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4382,13 +4449,13 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH22" t="n">
         <v>18</v>
@@ -4409,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
         <v>3</v>
@@ -4424,7 +4491,7 @@
         <v>28</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
@@ -4439,7 +4506,7 @@
         <v>28</v>
       </c>
       <c r="AX22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>16</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>11</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4621,7 +4688,7 @@
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>17</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.672</v>
+        <v>0.667</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4686,37 +4753,37 @@
         <v>83.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.497</v>
+        <v>0.496</v>
       </c>
       <c r="L24" t="n">
         <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P24" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U24" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="V24" t="n">
         <v>14.2</v>
@@ -4725,13 +4792,13 @@
         <v>6.7</v>
       </c>
       <c r="X24" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y24" t="n">
         <v>3.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA24" t="n">
         <v>20.8</v>
@@ -4740,13 +4807,13 @@
         <v>110</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>4</v>
@@ -4791,13 +4858,13 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4806,19 +4873,19 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
         <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>0.515</v>
+        <v>0.522</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J25" t="n">
         <v>79.3</v>
@@ -4874,28 +4941,28 @@
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O25" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P25" t="n">
         <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U25" t="n">
         <v>21</v>
@@ -4919,13 +4986,13 @@
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>22</v>
@@ -4964,19 +5031,19 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4985,10 +5052,10 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
         <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.463</v>
+        <v>0.455</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
         <v>6.2</v>
@@ -5059,13 +5126,13 @@
         <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
         <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.794</v>
@@ -5074,40 +5141,40 @@
         <v>10.3</v>
       </c>
       <c r="S26" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U26" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y26" t="n">
         <v>5.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA26" t="n">
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.9</v>
+        <v>101.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.2</v>
+        <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,10 +5186,10 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>20</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5152,10 +5219,10 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5167,7 +5234,7 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF27" t="n">
         <v>7</v>
@@ -5301,7 +5368,7 @@
         <v>7</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5337,7 +5404,7 @@
         <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,13 +5550,13 @@
         <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
@@ -5504,13 +5571,13 @@
         <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR28" t="n">
         <v>11</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>2.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>15</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG29" t="n">
         <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5677,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5704,13 +5771,13 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -5838,13 +5905,13 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5856,7 +5923,7 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5880,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
         <v>25</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
         <v>16</v>
@@ -6032,7 +6099,7 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6077,7 +6144,7 @@
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6089,7 +6156,7 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-18-2007-08</t>
+          <t>2008-03-18</t>
         </is>
       </c>
     </row>
